--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_price_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mobile/mobile_price_display.xlsx
@@ -452,36 +452,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>62.5</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Simple Display (Price is visible but not emphasized)</t>
+          <t>Bold Large (Price is the most prominent element)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>20.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Bold Large (Price is the most prominent element)</t>
+          <t>Simple Display (Price is visible but not emphasized)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C4" t="n">
-        <v>18.5</v>
+        <v>18.75</v>
       </c>
     </row>
   </sheetData>
